--- a/experiment/results/control-chart.xlsx
+++ b/experiment/results/control-chart.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,10 @@
     <font>
       <b val="1"/>
       <color rgb="00C0392B"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B9651F"/>
     </font>
     <font>
       <i val="1"/>
@@ -67,12 +71,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -924,29 +929,29 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
         <f>E2/B2</f>
         <v/>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
@@ -966,29 +971,29 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
         <f>E3/B3</f>
         <v/>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
@@ -1008,29 +1013,29 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
         <f>E4/B4</f>
         <v/>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
@@ -1050,10 +1055,10 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -1063,16 +1068,16 @@
         <v/>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
@@ -1092,29 +1097,29 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
         <f>E6/B6</f>
         <v/>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
@@ -1134,29 +1139,29 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
         <f>E7/B7</f>
         <v/>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
@@ -1176,10 +1181,10 @@
         <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1189,16 +1194,16 @@
         <v/>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
@@ -1218,29 +1223,29 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
         <f>E9/B9</f>
         <v/>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
@@ -1260,29 +1265,29 @@
         <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
         <f>E10/B10</f>
         <v/>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
@@ -1302,29 +1307,29 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2">
         <f>E11/B11</f>
         <v/>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
@@ -1348,29 +1353,29 @@
         <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2">
         <f>E12/B12</f>
         <v/>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
@@ -1390,29 +1395,29 @@
         <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2">
         <f>E13/B13</f>
         <v/>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
@@ -1432,29 +1437,29 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2">
         <f>E14/B14</f>
         <v/>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
@@ -1474,29 +1479,29 @@
         <v>50</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2">
         <f>E15/B15</f>
         <v/>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
@@ -1516,29 +1521,29 @@
         <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="2">
         <f>E16/B16</f>
         <v/>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
@@ -1558,29 +1563,29 @@
         <v>50</v>
       </c>
       <c r="C17" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="2">
         <f>E17/B17</f>
         <v/>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
@@ -1600,10 +1605,10 @@
         <v>50</v>
       </c>
       <c r="C18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
@@ -1613,16 +1618,16 @@
         <v/>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
@@ -1642,29 +1647,29 @@
         <v>50</v>
       </c>
       <c r="C19" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="2">
         <f>E19/B19</f>
         <v/>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
@@ -1684,31 +1689,35 @@
         <v>50</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F20" s="2">
         <f>E20/B20</f>
         <v/>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.13366</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>0.10479</v>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>異常：超出管制界限</t>
+        </is>
+      </c>
       <c r="L20" t="n">
         <v>7</v>
       </c>
@@ -1726,31 +1735,35 @@
         <v>50</v>
       </c>
       <c r="C21" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" s="2">
         <f>E21/B21</f>
         <v/>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.13366</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>0.10479</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>預警：3 點中 2 點超過 +2σ</t>
+        </is>
+      </c>
       <c r="L21" t="n">
         <v>6</v>
       </c>
@@ -1768,31 +1781,35 @@
         <v>50</v>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F22" s="2">
         <f>E22/B22</f>
         <v/>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.13366</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
+        <v>0.10479</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>異常：超出管制界限；預警：3 點中 2 點超過 +2σ</t>
+        </is>
+      </c>
       <c r="L22" t="n">
         <v>9</v>
       </c>
@@ -1810,31 +1827,35 @@
         <v>50</v>
       </c>
       <c r="C23" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F23" s="2">
         <f>E23/B23</f>
         <v/>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.13366</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
+        <v>0.10479</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>異常：超出管制界限；預警：3 點中 2 點超過 +2σ</t>
+        </is>
+      </c>
       <c r="L23" t="n">
         <v>8</v>
       </c>
@@ -1852,31 +1873,35 @@
         <v>50</v>
       </c>
       <c r="C24" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F24" s="2">
         <f>E24/B24</f>
         <v/>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.13366</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+        <v>0.10479</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>異常：超出管制界限；預警：3 點中 2 點超過 +2σ</t>
+        </is>
+      </c>
       <c r="L24" t="n">
         <v>14</v>
       </c>
@@ -1894,29 +1919,29 @@
         <v>50</v>
       </c>
       <c r="C25" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F25" s="2">
         <f>E25/B25</f>
         <v/>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -1940,29 +1965,29 @@
         <v>50</v>
       </c>
       <c r="C26" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F26" s="2">
         <f>E26/B26</f>
         <v/>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.06429</v>
+        <v>0.04571</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.16834</v>
+        <v>0.13433</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.13366</v>
+        <v>0.10479</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -1977,7 +2002,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>管制界限以 L01–L14（Phase I 基準期）計算；p̄ 與 σ = sqrt(p̄(1−p̄)/n)</t>
         </is>
@@ -1986,7 +2011,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>首次預警：L24；首次異常：L24</t>
+          <t>首次預警：L20；首次異常：L19</t>
         </is>
       </c>
     </row>
@@ -2029,10 +2054,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
@@ -2055,10 +2080,10 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
         <v>13</v>
-      </c>
-      <c r="C4" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -2068,10 +2093,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -2115,7 +2140,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -2124,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2143,7 +2168,7 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2178,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -2181,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -2191,7 +2216,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -2200,7 +2225,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2210,7 +2235,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -2219,7 +2244,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2238,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2257,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2267,7 +2292,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -2286,7 +2311,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -2305,7 +2330,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -2314,7 +2339,7 @@
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2333,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -2349,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -2362,7 +2387,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2371,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2381,13 +2406,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -2400,7 +2425,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2409,7 +2434,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2419,7 +2444,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -2438,16 +2463,16 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
         <v>3</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2457,7 +2482,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -2466,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2476,7 +2501,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -2485,7 +2510,7 @@
         <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2495,16 +2520,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2514,16 +2539,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2533,7 +2558,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -2542,7 +2567,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2552,7 +2577,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -2571,7 +2596,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -2580,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2595,7 +2620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -2660,7 +2685,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>判定層（主圖假設＝建議導入設計）：AI＋規則的判定依一致性分析「改善後」實測、按缺陷分類分開的混淆矩陣</t>
+          <t>判定層（主圖假設＝建議導入設計）：AI＋規則的判定依規範 v2.1 盲測第 1 次判定的混淆矩陣（不分缺陷分類）</t>
         </is>
       </c>
     </row>
@@ -2674,96 +2699,103 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AI 判 Pass（含漏判）直接放行、AI 判 Fail（含誤判）直接退件，不經人工 → 漏判率、誤判率維持改善後實測值。</t>
+          <t xml:space="preserve">  AI 判 Pass（含漏判）直接放行、AI 判 Fail（含誤判）直接退件，不經人工 → 漏判率、誤判率維持實測值。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>敏感度分析（另一工作表）：同一真實缺陷流程，但不做人工複判、AI＋規則判定即最終判定。</t>
+          <t>對照：第一輪規範 v1 的判定誤差（漏判 37%）跑同一批真實晶粒，結果見 control-chart-summary.json 的 v1Comparison。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  真實 Pass／— → AI 判定 Pass/Warning/Fail = 0.970, 0.000, 0.030</t>
+          <t>敏感度分析（另一工作表）：同一真實缺陷流程，但不做人工複判、AI＋規則判定即最終判定。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  真實 Warning／CHP → AI 判定 Pass/Warning/Fail = 0.667, 0.333, 0.000</t>
+          <t xml:space="preserve">  真實 Pass／— → AI 判定 Pass/Warning/Fail = 1.000, 0.000, 0.000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  真實 Warning／CRK → AI 判定 Pass/Warning/Fail = 0.519, 0.370, 0.111</t>
+          <t xml:space="preserve">  真實 Warning／CHP → AI 判定 Pass/Warning/Fail = 0.074, 0.926, 0.000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  真實 Warning／SCR → AI 判定 Pass/Warning/Fail = 0.000, 0.667, 0.333</t>
+          <t xml:space="preserve">  真實 Warning／CRK → AI 判定 Pass/Warning/Fail = 0.074, 0.926, 0.000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  真實 Warning／CON → AI 判定 Pass/Warning/Fail = 0.889, 0.111, 0.000</t>
+          <t xml:space="preserve">  真實 Warning／SCR → AI 判定 Pass/Warning/Fail = 0.074, 0.926, 0.000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  真實 Fail／CHP → AI 判定 Pass/Warning/Fail = 0.444, 0.000, 0.556</t>
+          <t xml:space="preserve">  真實 Warning／CON → AI 判定 Pass/Warning/Fail = 0.074, 0.926, 0.000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  真實 Fail／CRK → AI 判定 Pass/Warning/Fail = 0.167, 0.000, 0.833</t>
+          <t xml:space="preserve">  真實 Fail／CHP → AI 判定 Pass/Warning/Fail = 0.000, 0.000, 1.000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  真實 Fail／SCR → AI 判定 Pass/Warning/Fail = 0.333, 0.000, 0.667</t>
+          <t xml:space="preserve">  真實 Fail／CRK → AI 判定 Pass/Warning/Fail = 0.000, 0.000, 1.000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  真實 Fail／CON → AI 判定 Pass/Warning/Fail = 0.500, 0.000, 0.500</t>
+          <t xml:space="preserve">  真實 Fail／SCR → AI 判定 Pass/Warning/Fail = 0.000, 0.000, 1.000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>漏判率 = 0.370；誤判率 = 0.030（改善後實測，lots.json judgementErrorRates）</t>
+          <t xml:space="preserve">  真實 Fail／CON → AI 判定 Pass/Warning/Fail = 0.000, 0.000, 1.000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>判異規則：點超出 UCL → 異常；連續 7 點上升、或 3 點中 2 點超過 +2σ（同側）→ 預警。</t>
+          <t>漏判率 = 0.000；誤判率 = 0.000（實測，lots.json judgementErrorRates）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
+        <is>
+          <t>判異規則：點超出 UCL → 異常；連續 7 點上升、或 3 點中 2 點超過 +2σ（同側）→ 預警。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>柏拉圖：只計系統判定非 Pass 的晶粒上之 Warning／Fail 級缺陷；誤判晶粒依 AI 多報缺陷分類比例標記代碼。</t>
         </is>
@@ -2796,7 +2828,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CL = 0.0414；UCL = 0.1260；首次預警 = None；首次異常 = None</t>
+          <t>CL = 0.0400；UCL = 0.1231；首次預警 = 21；首次異常 = 22</t>
         </is>
       </c>
     </row>
@@ -2847,10 +2879,10 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>4</v>
@@ -2870,16 +2902,16 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
@@ -2893,16 +2925,16 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
@@ -2916,16 +2948,16 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
@@ -2939,16 +2971,16 @@
         <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
@@ -2962,16 +2994,16 @@
         <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
@@ -2985,16 +3017,16 @@
         <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -3008,16 +3040,16 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
@@ -3031,16 +3063,16 @@
         <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -3054,18 +3086,22 @@
         <v>50</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+        <v>0.16</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>異常：超出管制界限</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3077,16 +3113,16 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -3100,16 +3136,16 @@
         <v>50</v>
       </c>
       <c r="C15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
@@ -3123,16 +3159,16 @@
         <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr"/>
     </row>
@@ -3146,16 +3182,16 @@
         <v>50</v>
       </c>
       <c r="C17" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G17" t="inlineStr"/>
     </row>
@@ -3169,16 +3205,16 @@
         <v>50</v>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
@@ -3192,16 +3228,16 @@
         <v>50</v>
       </c>
       <c r="C19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
@@ -3215,16 +3251,16 @@
         <v>50</v>
       </c>
       <c r="C20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G20" t="inlineStr"/>
     </row>
@@ -3238,16 +3274,16 @@
         <v>50</v>
       </c>
       <c r="C21" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
@@ -3261,16 +3297,16 @@
         <v>50</v>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D22" t="n">
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="G22" t="inlineStr"/>
     </row>
@@ -3284,16 +3320,16 @@
         <v>50</v>
       </c>
       <c r="C23" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D23" t="n">
         <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
@@ -3307,18 +3343,22 @@
         <v>50</v>
       </c>
       <c r="C24" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>預警：3 點中 2 點超過 +2σ</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3330,18 +3370,22 @@
         <v>50</v>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D25" t="n">
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
+        <v>0.16</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>異常：超出管制界限；預警：3 點中 2 點超過 +2σ</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3353,18 +3397,22 @@
         <v>50</v>
       </c>
       <c r="C26" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>異常：超出管制界限；預警：3 點中 2 點超過 +2σ</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3376,18 +3424,22 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
+        <v>0.28</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>異常：超出管制界限；預警：3 點中 2 點超過 +2σ</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3399,18 +3451,22 @@
         <v>50</v>
       </c>
       <c r="C28" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+        <v>0.26</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>異常：超出管制界限；預警：3 點中 2 點超過 +2σ</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
